--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260503_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260503_203249.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
